--- a/result/train_info_googlenet_part_detrend_plr_stft_bin_win_fi.xlsx
+++ b/result/train_info_googlenet_part_detrend_plr_stft_bin_win_fi.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.381679069012802</v>
+        <v>0.3696629623557271</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1976315519557549</v>
+        <v>0.2007489876612227</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9227053140096618</v>
+        <v>0.9219620958751393</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9086676217765043</v>
+        <v>0.8996491228070176</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9403261675315048</v>
+        <v>0.9503335804299481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9242258652094718</v>
+        <v>0.9242970439798125</v>
       </c>
       <c r="I2" t="n">
-        <v>69.28348231315613</v>
+        <v>44.168048620224</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1568390368712294</v>
+        <v>0.1485172095383347</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1265120547176642</v>
+        <v>0.1043064586911902</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9511334076551468</v>
+        <v>0.9626532887402452</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9728155339805825</v>
+        <v>0.9705993215228044</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9284655300222387</v>
+        <v>0.9544106745737584</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9501232694860611</v>
+        <v>0.9624369276770697</v>
       </c>
       <c r="I3" t="n">
-        <v>69.88835740089417</v>
+        <v>43.23745512962341</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08522126018754685</v>
+        <v>0.07721618267279921</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09483264345047478</v>
+        <v>0.07607536070936045</v>
       </c>
       <c r="E4" t="n">
-        <v>0.966183574879227</v>
+        <v>0.9715719063545151</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9823619631901841</v>
+        <v>0.9635701275045537</v>
       </c>
       <c r="G4" t="n">
-        <v>0.949592290585619</v>
+        <v>0.980355819125278</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9656992084432717</v>
+        <v>0.9718905015616388</v>
       </c>
       <c r="I4" t="n">
-        <v>70.05986428260803</v>
+        <v>43.16638994216919</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06198931785343965</v>
+        <v>0.05922546079378841</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06370653245410711</v>
+        <v>0.05808321674066436</v>
       </c>
       <c r="E5" t="n">
-        <v>0.978446674098848</v>
+        <v>0.9788182831661093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9742836149889786</v>
+        <v>0.9802973977695167</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9829503335804299</v>
+        <v>0.9773906597479615</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9785977859778597</v>
+        <v>0.9788418708240535</v>
       </c>
       <c r="I5" t="n">
-        <v>70.13846778869629</v>
+        <v>43.30694770812988</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05097034078002818</v>
+        <v>0.03819825581965462</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06747781812039771</v>
+        <v>0.035913551967631</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9780750650315868</v>
+        <v>0.9879227053140096</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9640287769784173</v>
+        <v>0.9899516189058429</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9784592917123037</v>
+        <v>0.9879294336118849</v>
       </c>
       <c r="I6" t="n">
-        <v>69.94699287414551</v>
+        <v>43.41530108451843</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03335986602193445</v>
+        <v>0.03535072333744193</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03508306803187278</v>
+        <v>0.04114589653358128</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9881085098476403</v>
+        <v>0.9864362690449647</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9885014836795252</v>
+        <v>0.995096190116937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.977761304670126</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9881349647756766</v>
+        <v>0.9863525892690223</v>
       </c>
       <c r="I7" t="n">
-        <v>69.95868802070618</v>
+        <v>43.35428333282471</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02731287613537724</v>
+        <v>0.02753415362750554</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04390428199456211</v>
+        <v>0.05426145094541899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9851356373095503</v>
+        <v>0.9829059829059829</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9833825701624815</v>
+        <v>0.9847470238095238</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9870274277242401</v>
+        <v>0.9810971089696071</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9852016278209397</v>
+        <v>0.9829186780542146</v>
       </c>
       <c r="I8" t="n">
-        <v>69.97632527351379</v>
+        <v>46.2086615562439</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02703493488897164</v>
+        <v>0.02499455420724511</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03681703561850818</v>
+        <v>0.04265726596797602</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9888517279821628</v>
+        <v>0.9860646599777034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9820906432748538</v>
+        <v>0.9802270230684731</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9889584100110416</v>
+        <v>0.9861853011604347</v>
       </c>
       <c r="I9" t="n">
-        <v>69.54153370857239</v>
+        <v>46.57927012443542</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02196381498662856</v>
+        <v>0.02224677713401235</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04438328996614812</v>
+        <v>0.05373129275105287</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9843924191750278</v>
+        <v>0.9808621330360461</v>
       </c>
       <c r="F10" t="n">
-        <v>0.988050784167289</v>
+        <v>0.9942857142857143</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9807264640474426</v>
+        <v>0.9673832468495182</v>
       </c>
       <c r="H10" t="n">
-        <v>0.984375</v>
+        <v>0.9806500093931994</v>
       </c>
       <c r="I10" t="n">
-        <v>69.91737055778503</v>
+        <v>43.30914521217346</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02594122970027864</v>
+        <v>0.02427855989391569</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03237912264675282</v>
+        <v>0.02613068402019128</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9886659234485321</v>
+        <v>0.9901523597175771</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9925289503175196</v>
+        <v>0.9899962949240459</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9848035581912528</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9886511627906976</v>
+        <v>0.9901797294793404</v>
       </c>
       <c r="I11" t="n">
-        <v>69.53104472160339</v>
+        <v>43.30010581016541</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01941368901196305</v>
+        <v>0.01728927274939485</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04362806963276934</v>
+        <v>0.03228550716590883</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9871794871794872</v>
+        <v>0.9897807506503159</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9954768186958161</v>
+        <v>0.9947585174092101</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9788732394366197</v>
+        <v>0.9848035581912528</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9871052139786956</v>
+        <v>0.9897560067051593</v>
       </c>
       <c r="I12" t="n">
-        <v>69.52950692176819</v>
+        <v>43.45185112953186</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01791418177986811</v>
+        <v>0.02455316615601179</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03709308276956587</v>
+        <v>0.02337962135599551</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9881085098476403</v>
+        <v>0.9912671869193609</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9932584269662922</v>
+        <v>0.9936685288640595</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9829503335804299</v>
+        <v>0.9888806523350631</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9880774962742176</v>
+        <v>0.9912688092141928</v>
       </c>
       <c r="I13" t="n">
-        <v>69.48098707199097</v>
+        <v>43.54091763496399</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01939750754350409</v>
+        <v>0.01564084964795248</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03307532817958827</v>
+        <v>0.02477242983774332</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9896373056994818</v>
+        <v>0.9951528709917972</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9911045218680504</v>
+        <v>0.9892512972572276</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9903703703703703</v>
+        <v>0.9921933085501858</v>
       </c>
       <c r="I14" t="n">
-        <v>69.7014000415802</v>
+        <v>43.73077249526978</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01709867228775401</v>
+        <v>0.01759631567240616</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02124720123452176</v>
+        <v>0.02781121527601155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9947974730583427</v>
+        <v>0.989223337049424</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9922566371681416</v>
+        <v>0.993642483171279</v>
       </c>
       <c r="G15" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9848035581912528</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9948243992606285</v>
+        <v>0.9892032762472077</v>
       </c>
       <c r="I15" t="n">
-        <v>70.15508055686951</v>
+        <v>43.54300618171692</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01664272429727329</v>
+        <v>0.0161206264683034</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08173118331550536</v>
+        <v>0.04255111853387984</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9812337421033073</v>
+        <v>0.9871794871794872</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9931636916065325</v>
+        <v>0.9947308995107264</v>
       </c>
       <c r="G16" t="n">
-        <v>0.969236471460341</v>
+        <v>0.9796145292809488</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9810542112174077</v>
+        <v>0.9871148459383754</v>
       </c>
       <c r="I16" t="n">
-        <v>70.69624018669128</v>
+        <v>43.79499959945679</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01403424496004847</v>
+        <v>0.01662445580751122</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04915520123168365</v>
+        <v>0.02843798066164951</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9853214418431809</v>
+        <v>0.9910813823857302</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9844617092119867</v>
+        <v>0.9839298758217677</v>
       </c>
       <c r="G17" t="n">
-        <v>0.986286137879911</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9853730790594334</v>
+        <v>0.9911699779249448</v>
       </c>
       <c r="I17" t="n">
-        <v>71.09316301345825</v>
+        <v>43.26457715034485</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01715877457612627</v>
+        <v>0.01441122721166485</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02619142163924276</v>
+        <v>0.0300756911022145</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9920104050538833</v>
+        <v>0.9886659234485321</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.980678089682829</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9907338769458859</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9920207830766375</v>
+        <v>0.9887888255835324</v>
       </c>
       <c r="I18" t="n">
-        <v>71.87485694885254</v>
+        <v>43.39452981948853</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01644821995446236</v>
+        <v>0.01114015323752328</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0312798392387023</v>
+        <v>0.02390166262490882</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9927536231884058</v>
+        <v>0.9925678186547752</v>
       </c>
       <c r="F19" t="n">
-        <v>0.995527394707417</v>
+        <v>0.9900442477876106</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9927522765285263</v>
+        <v>0.9926062846580407</v>
       </c>
       <c r="I19" t="n">
-        <v>72.12891960144043</v>
+        <v>43.46020364761353</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01302564266356014</v>
+        <v>0.01270164382841584</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03274953572029856</v>
+        <v>0.02739389517434774</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9912671869193609</v>
+        <v>0.9895949461166852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9831748354059985</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9912785303395806</v>
+        <v>0.9896907216494846</v>
       </c>
       <c r="I20" t="n">
-        <v>72.82427406311035</v>
+        <v>43.26099967956543</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01295493928202421</v>
+        <v>0.01153603296278795</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0380566433666566</v>
+        <v>0.02342606111300989</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9910813823857302</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9842836257309941</v>
+        <v>0.9933358015549797</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9911667280088333</v>
+        <v>0.9938877569920356</v>
       </c>
       <c r="I21" t="n">
-        <v>73.29422450065613</v>
+        <v>43.38072967529297</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01156121890463992</v>
+        <v>0.01069228903598129</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03473556625120171</v>
+        <v>0.0191233661018013</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9894091415830546</v>
+        <v>0.9931252322556671</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9881700554528651</v>
+        <v>0.9936920222634509</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9907338769458859</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9894503053858967</v>
+        <v>0.9931392545892824</v>
       </c>
       <c r="I22" t="n">
-        <v>73.09076261520386</v>
+        <v>43.43019986152649</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.00838825501651231</v>
+        <v>0.009420994398139837</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02606845903365333</v>
+        <v>0.01632862770393385</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9944113263785395</v>
+        <v>0.9944485566247224</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9892512972572276</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9951851851851852</v>
       </c>
       <c r="I23" t="n">
-        <v>74.27111387252808</v>
+        <v>43.79025793075562</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00788109177249087</v>
+        <v>0.00882216198657561</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0400589313296718</v>
+        <v>0.03391254355273514</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9886659234485321</v>
+        <v>0.9899665551839465</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9867109634551495</v>
+        <v>0.992548435171386</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9907338769458859</v>
+        <v>0.9873980726464048</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9887183280932125</v>
+        <v>0.9899665551839465</v>
       </c>
       <c r="I24" t="n">
-        <v>73.80073618888855</v>
+        <v>43.09936738014221</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01142818540514536</v>
+        <v>0.01156225527655</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03157429284242722</v>
+        <v>0.01354133547661499</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9910813823857302</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9864170337738619</v>
+        <v>0.9981398809523809</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9911471781630394</v>
+        <v>0.9962866691422205</v>
       </c>
       <c r="I25" t="n">
-        <v>73.42948484420776</v>
+        <v>43.20020198822021</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01042620945108554</v>
+        <v>0.008904123325662733</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03693991575947034</v>
+        <v>0.02741686704914883</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9897807506503159</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9845984598459846</v>
+        <v>0.9878810135879544</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9898617511520738</v>
+        <v>0.9924368197749492</v>
       </c>
       <c r="I26" t="n">
-        <v>73.08103036880493</v>
+        <v>43.31613826751709</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.008107334408677355</v>
+        <v>0.009749595931219403</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07898240899047504</v>
+        <v>0.01676181892236004</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9860646599777034</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F27" t="n">
-        <v>0.994718973972086</v>
+        <v>0.9959062151097878</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9773906597479615</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9859786876051598</v>
+        <v>0.9938718662952646</v>
       </c>
       <c r="I27" t="n">
-        <v>72.70710563659668</v>
+        <v>43.23418021202087</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00855644379673976</v>
+        <v>0.006084199406991184</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03790079473272261</v>
+        <v>0.04522064938137945</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9875510962467484</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9951072638313888</v>
+        <v>0.9867695700110254</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9799851742031134</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9874883286647993</v>
+        <v>0.990957741280679</v>
       </c>
       <c r="I28" t="n">
-        <v>72.94580721855164</v>
+        <v>43.24848628044128</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01047642424708623</v>
+        <v>0.005772427404222402</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03831938543841108</v>
+        <v>0.01391730579697538</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9912671869193609</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9955140186915887</v>
+        <v>0.9937223042836041</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9870274277242401</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H29" t="n">
-        <v>0.991252559091755</v>
+        <v>0.9955604883462819</v>
       </c>
       <c r="I29" t="n">
-        <v>72.60932779312134</v>
+        <v>43.53876090049744</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.00519346853475617</v>
+        <v>0.005852095684469213</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03580588519397297</v>
+        <v>0.009009939767070702</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.99702712746191</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9962490622655664</v>
+        <v>0.9959319526627219</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9844329132690882</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9903057419835943</v>
+        <v>0.9970381340244354</v>
       </c>
       <c r="I30" t="n">
-        <v>72.86660933494568</v>
+        <v>43.45098423957825</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.007888020479404725</v>
+        <v>0.005674435101210302</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03158887018996894</v>
+        <v>0.01527605241665444</v>
       </c>
       <c r="E31" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9959123002601263</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9918518518518519</v>
+        <v>0.9966592427616926</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9922193404964802</v>
+        <v>0.995919881305638</v>
       </c>
       <c r="I31" t="n">
-        <v>72.68831729888916</v>
+        <v>43.20722794532776</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.008413630260867194</v>
+        <v>0.007085107756232696</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02912090119413932</v>
+        <v>0.02380152078850731</v>
       </c>
       <c r="E32" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9927536231884058</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9839181286549707</v>
+        <v>0.9970093457943925</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9885100074128984</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9907986750092014</v>
+        <v>0.9927414852037968</v>
       </c>
       <c r="I32" t="n">
-        <v>72.21328568458557</v>
+        <v>43.19608545303345</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.005615854913169765</v>
+        <v>0.006756696426909885</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01683939382196755</v>
+        <v>0.0140665154099036</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9929863418235512</v>
+        <v>0.9944485566247224</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9950064730904383</v>
+        <v>0.9951851851851852</v>
       </c>
       <c r="I33" t="n">
-        <v>72.22548604011536</v>
+        <v>43.27605938911438</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.00473964940720531</v>
+        <v>0.003465762695413257</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03838904183980716</v>
+        <v>0.02459398009959195</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9933085501858736</v>
+        <v>0.9900698786318499</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9903632320237212</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H34" t="n">
-        <v>0.991833704528582</v>
+        <v>0.9939080671958649</v>
       </c>
       <c r="I34" t="n">
-        <v>71.83923316001892</v>
+        <v>43.38460063934326</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.008275304722796147</v>
+        <v>0.006738204244882589</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03819333482387313</v>
+        <v>0.01791263182561248</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9897807506503159</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9943883277216611</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9851742031134173</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9897598212623347</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="I35" t="n">
-        <v>72.3339147567749</v>
+        <v>43.23246002197266</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.005769246576040403</v>
+        <v>0.006223912025480268</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0413629566134697</v>
+        <v>0.01776406836201118</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9905239687848384</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9932910920611256</v>
+        <v>0.9948148148148148</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9905222077680729</v>
+        <v>0.9951834012597258</v>
       </c>
       <c r="I36" t="n">
-        <v>72.01600551605225</v>
+        <v>43.19314575195312</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.008085320738103509</v>
+        <v>0.004241669082055045</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0234762812016505</v>
+        <v>0.01290360002237251</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9918759231905465</v>
+        <v>0.9970304380103935</v>
       </c>
       <c r="G37" t="n">
         <v>0.9955522609340252</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9937106918238994</v>
+        <v>0.9962908011869436</v>
       </c>
       <c r="I37" t="n">
-        <v>71.725426197052</v>
+        <v>43.47130107879639</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.00539760157093742</v>
+        <v>0.003080397961079235</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.02322800948515912</v>
+        <v>0.01516404763671378</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9942400594574508</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9944382647385984</v>
+        <v>0.9959259259259259</v>
       </c>
       <c r="G38" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9942539388322521</v>
+        <v>0.9962949240459429</v>
       </c>
       <c r="I38" t="n">
-        <v>71.90408396720886</v>
+        <v>43.17869114875793</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.002787976637182307</v>
+        <v>0.004689498805178585</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.02829782169085091</v>
+        <v>0.01785380676758867</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9899665551839465</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9940209267563528</v>
+        <v>0.9955588452997779</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9859154929577465</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9899516189058429</v>
+        <v>0.9962962962962963</v>
       </c>
       <c r="I39" t="n">
-        <v>71.60029220581055</v>
+        <v>43.1800684928894</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.005930047128097857</v>
+        <v>0.0001202695952838811</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0188348122567048</v>
+        <v>0.01716600759403683</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9951690821256038</v>
+        <v>0.99702712746191</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9966666666666667</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9970359392367544</v>
       </c>
       <c r="I40" t="n">
-        <v>71.63553261756897</v>
+        <v>43.10670495033264</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.003267195764309465</v>
+        <v>1.70771994663296e-05</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02224896364601892</v>
+        <v>0.02345740860280108</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9951690821256038</v>
+        <v>0.9973987365291713</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9962852897473997</v>
+        <v>0.9970370370370371</v>
       </c>
       <c r="G41" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9951762523191094</v>
+        <v>0.9974064468321601</v>
       </c>
       <c r="I41" t="n">
-        <v>72.01018357276917</v>
+        <v>43.16483807563782</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.005506537486904525</v>
+        <v>0.007196383138876224</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0202762685199753</v>
+        <v>0.01440149485304939</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9942400594574508</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9926117473217584</v>
+        <v>0.9940762680488708</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9942645698427383</v>
+        <v>0.9946286349323948</v>
       </c>
       <c r="I42" t="n">
-        <v>72.68474268913269</v>
+        <v>43.12741637229919</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.005436072841639056</v>
+        <v>0.006936578246506439</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02214536340219229</v>
+        <v>0.0114251946741195</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9926062846580407</v>
+        <v>0.9948301329394387</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9938922820655192</v>
+        <v>0.9966703662597114</v>
       </c>
       <c r="I43" t="n">
-        <v>72.8971745967865</v>
+        <v>43.14503812789917</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.003008733495841813</v>
+        <v>0.002050064568253114</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01986271775262914</v>
+        <v>0.01079458239799878</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9953548866592344</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9962866691422205</v>
+        <v>0.9944608567208272</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9953626414394361</v>
+        <v>0.9963004069552349</v>
       </c>
       <c r="I44" t="n">
-        <v>72.85263419151306</v>
+        <v>43.40248274803162</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.004393060471609669</v>
+        <v>0.00327439999538213</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.023523189319467</v>
+        <v>0.01506909128572675</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9951690821256038</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9948148148148148</v>
+        <v>0.9951834012597258</v>
       </c>
       <c r="G45" t="n">
         <v>0.9955522609340252</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9951834012597258</v>
+        <v>0.9953677969242172</v>
       </c>
       <c r="I45" t="n">
-        <v>72.32962846755981</v>
+        <v>42.98905968666077</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0004827143944363683</v>
+        <v>0.002480406493720273</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.03136350077386194</v>
+        <v>0.01683891717822497</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9970227018980276</v>
+        <v>0.9951958610495196</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9929577464788732</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9949860724233983</v>
+        <v>0.9966691339748335</v>
       </c>
       <c r="I46" t="n">
-        <v>72.50249886512756</v>
+        <v>43.10258555412292</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.001333348039689685</v>
+        <v>0.003590933749565943</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.02276674253261674</v>
+        <v>0.02459213969811609</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9951940850277264</v>
+        <v>0.9973782771535581</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9870274277242401</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9964834351286322</v>
+        <v>0.9921758569299552</v>
       </c>
       <c r="I47" t="n">
-        <v>72.73142433166504</v>
+        <v>43.3309919834137</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.002301299027342987</v>
+        <v>0.002375391025149986</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.03869494917490992</v>
+        <v>0.02354326548313445</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9951492537313433</v>
+        <v>0.9904235727440147</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9885100074128984</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9918185198958721</v>
+        <v>0.9935340846111214</v>
       </c>
       <c r="I48" t="n">
-        <v>73.0973801612854</v>
+        <v>43.12117576599121</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.007982833899479123</v>
+        <v>0.001993514117794637</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.02609694200346092</v>
+        <v>0.01667779974893041</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9955257270693513</v>
+        <v>0.9970304380103935</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9896219421793921</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9925650557620818</v>
+        <v>0.9962908011869436</v>
       </c>
       <c r="I49" t="n">
-        <v>72.19729709625244</v>
+        <v>43.16974425315857</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.002766422722633837</v>
+        <v>0.006398576800540095</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.01759968657107713</v>
+        <v>0.01462730550361844</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9955555555555555</v>
+        <v>0.9962962962962963</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9959244164505372</v>
+        <v>0.9966654316413487</v>
       </c>
       <c r="I50" t="n">
-        <v>72.1519079208374</v>
+        <v>43.03938865661621</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.002945930806655819</v>
+        <v>0.003385645224171406</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01859023065102541</v>
+        <v>0.01737247186845965</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9955406911928651</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9966567607726597</v>
+        <v>0.9933505725895826</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9955473098330241</v>
+        <v>0.995004625346901</v>
       </c>
       <c r="I51" t="n">
-        <v>71.90681648254395</v>
+        <v>43.26129460334778</v>
       </c>
     </row>
   </sheetData>
